--- a/output/full_scan/batch_seq8_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-12.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>973.679781345255</v>
+        <v>1088.679781345255</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>376</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.32751323264429</v>
+        <v>63.32751325535119</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30.60728950129867</v>
+        <v>30.60728952286802</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.455221924658408</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.0521080425071742</v>
+        <v>-0.0521080437089525</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7751</v>
+        <v>6924</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>904.1530293232324</v>
+        <v>1071.655118287595</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1640</v>
+        <v>146.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.00422789258076</v>
+        <v>66.61429315130479</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.87127579001122</v>
+        <v>30.5991883359067</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.014118316119863</v>
+        <v>2.045737214433004</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>13.0689046895801</v>
+        <v>-0.0353963912337649</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6924</v>
+        <v>6909</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>901.6551182875947</v>
+        <v>1049.787654254944</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>146.5</v>
+        <v>47.85</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.61429316484002</v>
+        <v>70.9350847055252</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.59918826952141</v>
+        <v>26.68819956524274</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.045737214433004</v>
+        <v>1.94009339953899</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.0353963910174641</v>
+        <v>0.4378937807622768</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6916</v>
+        <v>7751</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>815.7696580147717</v>
+        <v>1019.153029323232</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19.45</v>
+        <v>1640</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,29 +711,29 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.62106629011367</v>
+        <v>58.00422790843498</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.68162745328338</v>
+        <v>14.87127579854864</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.292184556779429</v>
+        <v>1.014118316119863</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1125044278674962</v>
+        <v>13.06890468837824</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>807.5346223733641</v>
+        <v>977.534622373364</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>80.90000000000001</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>66.50693394068315</v>
+        <v>66.50693390052717</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.83006165289288</v>
+        <v>15.83006166810415</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.13948033270694</v>
@@ -786,27 +786,27 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7792</v>
+        <v>6918</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>772.0306125145898</v>
+        <v>965.860895120923</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>411</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.72405923644689</v>
+        <v>58.15110990347812</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>53.02628488342423</v>
+        <v>31.70205623289711</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7238858467233427</v>
+        <v>0.6796965832232961</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.591570120420635</v>
+        <v>0.09260101270641399</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6909</v>
+        <v>6925</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>769.7876542549444</v>
+        <v>944.6056373991124</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.85</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70.93508480960148</v>
+        <v>74.01604438660391</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.68819951891185</v>
+        <v>42.35039415140039</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.94009339953899</v>
+        <v>2.06056373991123</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4378937807382417</v>
+        <v>0.9402020883777862</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6913</v>
+        <v>6916</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>752.1951644352397</v>
+        <v>930.7696580147716</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>142</v>
+        <v>19.45</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.32604370453609</v>
+        <v>61.62106620173704</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.86358302111357</v>
+        <v>24.68162740630257</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.01688488610683</v>
+        <v>2.292184556779429</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.360732599763207</v>
+        <v>0.1125044278434589</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6863</v>
+        <v>6913</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>746.0423905315574</v>
+        <v>922.19516443524</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>102.5</v>
+        <v>142</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.41379643272322</v>
+        <v>61.32604354276157</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.56681833499575</v>
+        <v>16.86358306551391</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.357652168575683</v>
+        <v>5.01688488610683</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.047481473768671</v>
+        <v>1.360732600364087</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6925</v>
+        <v>6863</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>744.6056373991123</v>
+        <v>916.0423905315574</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>74.01604493058394</v>
+        <v>57.41379651988925</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>42.35039369345042</v>
+        <v>23.56681836123357</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.06056373991123</v>
+        <v>2.357652168575683</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9402020851331132</v>
+        <v>1.04748147292746</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6918</v>
+        <v>7769</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>740.8608951209227</v>
+        <v>865.9245981150865</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>6490</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.15111002266433</v>
+        <v>59.41390963939133</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.70205623289711</v>
+        <v>12.96891498622636</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6796965832232961</v>
+        <v>1.856507767758135</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0926010128025464</v>
+        <v>53.37680577836991</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7711</v>
+        <v>7734</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>737.9823908505425</v>
+        <v>837.2458345715598</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>612</v>
+        <v>2915</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.60144715969814</v>
+        <v>56.63865981733001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.59519873926161</v>
+        <v>14.08486064205241</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.758581051591889</v>
+        <v>1.698531868596432</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.683172847596751</v>
+        <v>34.71666691646668</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7734</v>
+        <v>6901</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>722.2458345715603</v>
+        <v>808.4165930185592</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2915</v>
+        <v>18.05</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.6386598504465</v>
+        <v>64.73989564633223</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.08486063217944</v>
+        <v>28.41252226024196</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.698531868596432</v>
+        <v>1.460359007300073</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>34.71666691646668</v>
+        <v>0.2488532164721045</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>691.366748356223</v>
+        <v>806.3667483562228</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>192.5</v>
@@ -1244,7 +1244,7 @@
         <v>59.13018998253454</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>35.0168346891159</v>
+        <v>35.01683464945063</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>2.032342975319965</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.064798678357806</v>
+        <v>2.064798677276259</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6861</v>
+        <v>6903</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>684.9312121845372</v>
+        <v>795.3801787427326</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>275.5</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.31169696862918</v>
+        <v>62.73756336244161</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.02872544408145</v>
+        <v>19.72597349425687</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6072836257574342</v>
+        <v>2.676861741548957</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.9424930401162436</v>
+        <v>3.386557992631</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7712</v>
+        <v>7792</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>674.8077331088302</v>
+        <v>772.0306125145898</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>168</v>
+        <v>411</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.18608447647765</v>
+        <v>62.72405923955434</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.56475245381985</v>
+        <v>53.02628484603608</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8423428609163798</v>
+        <v>0.7238858467233427</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.788640463260263</v>
+        <v>-1.591570121382055</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6937</v>
+        <v>7556</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>669.6108589347625</v>
+        <v>751.7231124363381</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>291.5</v>
+        <v>286</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.23828911211713</v>
+        <v>62.16589932740021</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.94899380879885</v>
+        <v>35.58041912214475</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4510460254776332</v>
+        <v>0.6691687566203738</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.140124888046495</v>
+        <v>2.507686710964997</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6903</v>
+        <v>7711</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>655.3801787427299</v>
+        <v>727.9823908505425</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>332</v>
+        <v>612</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62.7375633716828</v>
+        <v>58.60144715626178</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.72597351821299</v>
+        <v>31.59519887286687</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.676861741548957</v>
+        <v>1.758581051591889</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>3.38655799215033</v>
+        <v>2.683172846875724</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6933</v>
+        <v>6988</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>638.0902222093379</v>
+        <v>723.6570298224915</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>382.5</v>
+        <v>12.85</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.77784027382859</v>
+        <v>61.81768834130489</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46.04451058637208</v>
+        <v>18.33626596257086</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3639894418400974</v>
+        <v>0.9834786696861616</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.244951741142998</v>
+        <v>0.1333434568689523</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7810</v>
+        <v>6861</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>623.989276996194</v>
+        <v>684.9312121845372</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>237</v>
+        <v>275.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.95092928016923</v>
+        <v>58.31169695001777</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36.8887133613593</v>
+        <v>38.02872541547798</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9056582677119288</v>
+        <v>0.6072836257574342</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.7474770623920648</v>
+        <v>-0.9424930397076708</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7556</v>
+        <v>7839</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>611.7231124363379</v>
+        <v>681.3601055662613</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>286</v>
+        <v>44.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.16589951650936</v>
+        <v>56.81056776507958</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>35.58041914389354</v>
+        <v>25.5018836018509</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6691687566203738</v>
+        <v>0.5581482610632958</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.507686708921987</v>
+        <v>0.2172659824956334</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6953</v>
+        <v>6944</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>601.1567965591171</v>
+        <v>676.4494140751501</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>250</v>
+        <v>837</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.82361943987198</v>
+        <v>62.07732590590862</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.82455728434465</v>
+        <v>32.75915549715468</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4556289034483768</v>
+        <v>1.257517192733575</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.9924454860957166</v>
+        <v>14.91569017133931</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6870</v>
+        <v>7712</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>596.4475562277993</v>
+        <v>674.8077331088302</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>315</v>
+        <v>168</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.06043529501469</v>
+        <v>57.18608443762803</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.85165009407115</v>
+        <v>31.56475250058434</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3644923458782774</v>
+        <v>0.8423428609163798</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.227489479716684</v>
+        <v>0.7886404643418352</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7795</v>
+        <v>6937</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>593.1899573162384</v>
+        <v>669.6108589347625</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>532</v>
+        <v>291.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.56892823188271</v>
+        <v>49.23828897954437</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>20.93030114688163</v>
+        <v>26.94899383212542</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.434271461470377</v>
+        <v>0.4510460254776332</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.566044017451962</v>
+        <v>-2.140124887325455</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8028</v>
+        <v>6971</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>592.2090759082289</v>
+        <v>659.3433587610044</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>281.5</v>
+        <v>24.45</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.27841669887043</v>
+        <v>49.87410981777887</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.99542252983004</v>
+        <v>26.48113525534656</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2418626091803468</v>
+        <v>1.256668289242323</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.549219143550508</v>
+        <v>0.1219455444187819</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6902</v>
+        <v>6933</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>591.3148808209011</v>
+        <v>648.0902222093379</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>136</v>
+        <v>382.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44.85666394543491</v>
+        <v>63.7778402860043</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.01730336619364</v>
+        <v>46.04451061684046</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3112057092051295</v>
+        <v>0.3639894418400974</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-2.817115324109686</v>
+        <v>-2.244951742825436</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7839</v>
+        <v>7810</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>566.3601055662613</v>
+        <v>623.989276996194</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>44.5</v>
+        <v>237</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.81056776507958</v>
+        <v>56.9509292584266</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.50188361154612</v>
+        <v>36.88871338226025</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5581482610632958</v>
+        <v>0.9056582677119288</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2172659824956334</v>
+        <v>0.7474770625122424</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6838</v>
+        <v>7788</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>561.5510831218114</v>
+        <v>623.1493325209904</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>25.1</v>
+        <v>316</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.72216882874896</v>
+        <v>54.10001353947885</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.66127691511953</v>
+        <v>21.93659694140634</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5861208963447826</v>
+        <v>0.9933959861236612</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0224988964952377</v>
+        <v>1.274546060736213</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7744</v>
+        <v>7765</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>560.8021476871365</v>
+        <v>613.7145345862544</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>506</v>
+        <v>237</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.91923718536936</v>
+        <v>55.74754949800266</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.98316327937525</v>
+        <v>32.69511463296087</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9056904857720408</v>
+        <v>0.3039317477129957</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-3.650648935141874</v>
+        <v>-0.4833877750454993</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7769</v>
+        <v>6953</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>550.9245981150865</v>
+        <v>601.156796559117</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6490</v>
+        <v>250</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.41390962466954</v>
+        <v>56.82361934065761</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12.96891495169888</v>
+        <v>23.82455736963196</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.856507767758135</v>
+        <v>0.4556289034483768</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>53.3768057771682</v>
+        <v>0.9924454869369236</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7799</v>
+        <v>6870</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>550.9150612171329</v>
+        <v>596.4475562277992</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>496</v>
+        <v>315</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.73166470591848</v>
+        <v>54.06043531590426</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>43.66000211946913</v>
+        <v>32.85165012245796</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6243674344965329</v>
+        <v>0.3644923458782774</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-4.336114819854856</v>
+        <v>-2.227489480678077</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6944</v>
+        <v>7631</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>536.44941407515</v>
+        <v>594.9141063435444</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>837</v>
+        <v>139</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>62.07732593224438</v>
+        <v>46.82022803471311</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.75915550323787</v>
+        <v>21.9905906006505</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.257517192733575</v>
+        <v>0.7181742179668373</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>14.91569016941655</v>
+        <v>0.06544989668898089</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7717</v>
+        <v>7795</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>533.6380704874949</v>
+        <v>593.1899573162384</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.08477708776244</v>
+        <v>53.56892822974133</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.34992393051328</v>
+        <v>20.93030113599104</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3659943953451277</v>
+        <v>0.434271461470377</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>1</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-5.792268004097274</v>
+        <v>3.566044017091404</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6922</v>
+        <v>8028</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>527.8498660822728</v>
+        <v>592.209075908229</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>203</v>
+        <v>281.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.06363086516102</v>
+        <v>60.27841664586382</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20.4463565236333</v>
+        <v>28.99542252621632</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6249830952239274</v>
+        <v>0.2418626091803468</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.7741386207677596</v>
+        <v>2.549219143790888</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6971</v>
+        <v>6902</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>519.3433587610044</v>
+        <v>591.3148808209011</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>24.45</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.87410980535289</v>
+        <v>44.85666391895465</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.48113520414336</v>
+        <v>25.0173033939519</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.256668289242323</v>
+        <v>0.3112057092051295</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1219455444187819</v>
+        <v>-2.817115323869335</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7788</v>
+        <v>6965</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>518.1493325209904</v>
+        <v>566.8155688352706</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>316</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.10001355623354</v>
+        <v>44.65760065166544</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.93659683186623</v>
+        <v>46.70687376671072</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9933959861236612</v>
+        <v>1.200342706255794</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.27454606001516</v>
+        <v>0.1236861264575588</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7765</v>
+        <v>6838</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>498.7145345862544</v>
+        <v>561.5510831218114</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>237</v>
+        <v>25.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.74754953690096</v>
+        <v>56.72216881603672</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>32.69511460602524</v>
+        <v>32.66127687295782</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3039317477129957</v>
+        <v>0.5861208963447826</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4833877754060092</v>
+        <v>-0.0224988965312954</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6877</v>
+        <v>7744</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>492.0641661716832</v>
+        <v>560.8021476871365</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>140.5</v>
+        <v>506</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>60.73761173975635</v>
+        <v>46.91923717255912</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.44289111528564</v>
+        <v>23.98316323548856</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.725812606026433</v>
+        <v>0.9056904857720408</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.313588399170946</v>
+        <v>-3.650648935382153</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7747</v>
+        <v>8016</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>490.445675529419</v>
+        <v>554.3038427558948</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.65400781223421</v>
+        <v>53.55834737260541</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7.346705115752393</v>
+        <v>11.67542718921995</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.0267273304977264</v>
+        <v>0.7330967555697622</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0378059124215426</v>
+        <v>1.50329331744599</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7827</v>
+        <v>7799</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>484.3626029953948</v>
+        <v>550.9150612171329</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>167</v>
+        <v>496</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.08265899362755</v>
+        <v>54.73166465090122</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.81582789688633</v>
+        <v>43.66000215492219</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.998219687589571</v>
+        <v>0.6243674344965329</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.6674171789099814</v>
+        <v>-4.336114819614536</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6901</v>
+        <v>7717</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>483.4165930185592</v>
+        <v>533.6380704874949</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>18.05</v>
+        <v>553</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>64.73989571744906</v>
+        <v>52.08477708776244</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.41252221393313</v>
+        <v>18.34992393051328</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.460359007300073</v>
+        <v>0.3659943953451277</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2488532164240343</v>
+        <v>-5.792268004097274</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6885</v>
+        <v>7610</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>471.5901407633591</v>
+        <v>528.0303510391107</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>28.9</v>
+        <v>1635</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.36550874134827</v>
+        <v>42.12134309972144</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>50.69615547756664</v>
+        <v>10.23824067805718</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4072679009037614</v>
+        <v>0.8172270818421644</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.4196400939073266</v>
+        <v>-18.6909501461588</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7704</v>
+        <v>6922</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>468.5550983576401</v>
+        <v>527.8498660822728</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>61.4</v>
+        <v>203</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.52156010231877</v>
+        <v>49.06363087843824</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.60663290559084</v>
+        <v>20.44635651184014</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.233629032546804</v>
+        <v>0.6249830952239274</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0042579816358714</v>
+        <v>-0.7741386211282646</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6947</v>
+        <v>6983</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>466.7507858927447</v>
+        <v>522.9903383426678</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>68.8</v>
+        <v>374.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.63050053239801</v>
+        <v>62.045893060884</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.90797032855464</v>
+        <v>30.40299405282318</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.615694003007674</v>
+        <v>1.343020534927242</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3397072958989485</v>
+        <v>1.968478001645746</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7772</v>
+        <v>6869</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>465.2249872454174</v>
+        <v>520.0036728151929</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>132</v>
+        <v>70.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>43.73019111175169</v>
+        <v>56.95513994600746</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45.14735263578458</v>
+        <v>21.44765345144373</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4224987245417413</v>
+        <v>0.5451798393799875</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-6.370618192679498</v>
+        <v>0.1732176903841555</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7703</v>
+        <v>8011</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>464.9855967751621</v>
+        <v>511.3884303145846</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>198</v>
+        <v>16.45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.57506665686197</v>
+        <v>55.73534614790542</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.88265070785427</v>
+        <v>30.69994622070006</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.072874984842973</v>
+        <v>0.756186348917974</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.834530692716104</v>
+        <v>0.0940855286883574</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7610</v>
+        <v>7740</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>453.0303510391108</v>
+        <v>496.6452979623601</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1635</v>
+        <v>115</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>42.12134311527701</v>
+        <v>46.89927524837504</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.2382408730782</v>
+        <v>26.68354729771584</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8172270818421644</v>
+        <v>3.288829540640118</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-18.69095014976397</v>
+        <v>1.349599329934534</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6988</v>
+        <v>6906</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>448.6570298224915</v>
+        <v>495.0879749577384</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>12.85</v>
+        <v>79</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.81768900749127</v>
+        <v>45.31111036674484</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.33626610507495</v>
+        <v>32.87604527199728</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9834786696861616</v>
+        <v>0.2696049086246432</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.133343456508431</v>
+        <v>-0.7781709414137592</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6910</v>
+        <v>6877</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>442.1769470127432</v>
+        <v>492.0641661716838</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>25.5</v>
+        <v>140.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.63981554135609</v>
+        <v>60.7376116614093</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30.41261766731452</v>
+        <v>22.44289112874257</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4099152488370611</v>
+        <v>1.725812606026433</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0746601430400696</v>
+        <v>1.313588399243043</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8016</v>
+        <v>7747</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>439.3038427558948</v>
+        <v>490.445675529419</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.55834735220574</v>
+        <v>51.654007808575</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.67542712420212</v>
+        <v>7.346705142174807</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7330967555697622</v>
+        <v>0.0267273304977264</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.50329331804687</v>
+        <v>0.0378059121811985</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6859</v>
+        <v>6862</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>438.273428594144</v>
+        <v>490.3384904340292</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.21949204850847</v>
+        <v>59.66248694740941</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>37.25993673367137</v>
+        <v>19.36506295720403</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.022182926668338</v>
+        <v>1.204358989911243</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.6888162537961784</v>
+        <v>1.445147306325955</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8033</v>
+        <v>7855</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>434.4709698005377</v>
+        <v>486.4777689447498</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>168</v>
+        <v>41.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.81587518371496</v>
+        <v>22.87504610261987</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7.807245346167943</v>
+        <v>58.75207589623036</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7372127781953308</v>
+        <v>0.5595113137818786</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3639299023265687</v>
+        <v>0.850016678802807</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6869</v>
+        <v>7827</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>410.003672815193</v>
+        <v>484.3626029953951</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>70.5</v>
+        <v>167</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.95513991289224</v>
+        <v>62.08265914348039</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.44765342090403</v>
+        <v>16.81582799895013</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5451798393799875</v>
+        <v>0.998219687589571</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1732176906245027</v>
+        <v>0.6674171778765028</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7631</v>
+        <v>6895</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>409.9141063435444</v>
+        <v>482.6620770593845</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>139</v>
+        <v>153.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.82022809642567</v>
+        <v>57.47300196523355</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.99059047029348</v>
+        <v>15.90394705021756</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7181742179668373</v>
+        <v>0.8352456703571648</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0654498976503796</v>
+        <v>0.3353631692656069</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8011</v>
+        <v>6885</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>396.3884303145846</v>
+        <v>471.5901407633591</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>16.45</v>
+        <v>28.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.73534654853534</v>
+        <v>53.36550876299737</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30.69994601566263</v>
+        <v>50.69615547924414</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.756186348917974</v>
+        <v>0.4072679009037614</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0940855285801999</v>
+        <v>-0.4196400938953082</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6840</v>
+        <v>7704</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>392.1585367849339</v>
+        <v>468.5550983576401</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>92</v>
+        <v>61.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.69147925614127</v>
+        <v>50.52156007895079</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.56231185112683</v>
+        <v>16.60663305106338</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5716534337325131</v>
+        <v>2.233629032546804</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.759048065493421</v>
+        <v>-0.004257981792099</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6955</v>
+        <v>6947</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>390.831143134348</v>
+        <v>466.7507858927447</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>93.2</v>
+        <v>68.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.63683585411457</v>
+        <v>48.63050039256676</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5.453394956044301</v>
+        <v>10.9079702536769</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2775183075091092</v>
+        <v>1.615694003007674</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.750873034407479</v>
+        <v>0.3397072960431584</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6862</v>
+        <v>7772</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>385.3384904340278</v>
+        <v>465.2249872454174</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>59.66248686108391</v>
+        <v>43.73019112854311</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.36506287757781</v>
+        <v>45.14735273921762</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.204358989911243</v>
+        <v>0.4224987245417413</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.445147307287335</v>
+        <v>-6.370618193424564</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6906</v>
+        <v>7703</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>385.0879749577384</v>
+        <v>464.9855967751621</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.3111103874885</v>
+        <v>49.57506633856506</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.87604529448654</v>
+        <v>29.88265081043003</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2696049086246432</v>
+        <v>1.072874984842973</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.7781709414137592</v>
+        <v>-0.8345306898319524</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6983</v>
+        <v>7821</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>382.9903383426677</v>
+        <v>450.35427564423</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>374.5</v>
+        <v>36.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>62.04589304680545</v>
+        <v>46.41156465067643</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>30.40299399488056</v>
+        <v>35.66988130142813</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.343020534927242</v>
+        <v>1.872107782621567</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.968478001645746</v>
+        <v>-0.0427356340445073</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7736</v>
+        <v>6910</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>375.4404834088279</v>
+        <v>442.1769470127429</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.64434849240754</v>
+        <v>49.6398151757032</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.36738689256876</v>
+        <v>30.41261784278101</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.44608102704864</v>
+        <v>0.4099152488370611</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1456393292738918</v>
+        <v>-0.0746601426675317</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7547</v>
+        <v>7738</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>369.4596456692913</v>
+        <v>441.7208012606401</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>58.6</v>
+        <v>162</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.46491877379579</v>
+        <v>52.91398540273693</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.60852816996951</v>
+        <v>15.47528790105503</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3459645669291338</v>
+        <v>0.8401988701392641</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1785787302717194</v>
+        <v>0.6847760856359204</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6895</v>
+        <v>6859</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>367.6620770593845</v>
+        <v>438.2734285941442</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>153.5</v>
+        <v>116</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>57.4730022373433</v>
+        <v>46.21949197197541</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.90394693546695</v>
+        <v>37.25993675371644</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8352456703571648</v>
+        <v>1.022182926668338</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.3353631680639033</v>
+        <v>-0.6888162541566851</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6919</v>
+        <v>8033</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>363.432004611126</v>
+        <v>434.4709698005377</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>77.2</v>
+        <v>168</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>32.64575374613277</v>
+        <v>41.81587521964585</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.35759031462548</v>
+        <v>7.807245317723212</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4697079789208124</v>
+        <v>0.7372127781953308</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.4308944730088448</v>
+        <v>0.3639299011248451</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7750</v>
+        <v>6949</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>361.1417718116325</v>
+        <v>425.1643450613371</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1915</v>
+        <v>46.7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.60214767039854</v>
+        <v>25.98416132895341</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.3512616414676</v>
+        <v>45.44809243672957</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.12077332553824</v>
+        <v>0.555496172948613</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>10.56163794428753</v>
+        <v>31.85810539998843</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7856</v>
+        <v>6955</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>360.8098086489869</v>
+        <v>410.831143134348</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>3835</v>
+        <v>93.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>36.31332380901144</v>
+        <v>48.63683586319067</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.54883144717722</v>
+        <v>5.453394667458402</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.151578047471147</v>
+        <v>0.2775183075091092</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-80.65921042144876</v>
+        <v>0.7508730340469576</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7805</v>
+        <v>6840</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>351.593853940262</v>
+        <v>392.1585367849339</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>491</v>
+        <v>92</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.79340593824967</v>
+        <v>44.69147924738721</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.80143902273723</v>
+        <v>26.56231189559442</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.838598737424477</v>
+        <v>0.5716534337325131</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>4.36930801023702</v>
+        <v>-1.759048065637626</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6907</v>
+        <v>7722</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>342.7709492182713</v>
+        <v>380.655472171428</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>181.5</v>
+        <v>265</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.90177964232763</v>
+        <v>47.41092048302833</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.25118803316159</v>
+        <v>15.13911557419686</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2835132485385495</v>
+        <v>0.5196400801855945</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.509111356590281</v>
+        <v>1.387066980956992</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7768</v>
+        <v>6890</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>326.264316279618</v>
+        <v>379.0416352018341</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>292.5</v>
+        <v>152</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.55691331653948</v>
+        <v>47.35160971203268</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>26.27506444014929</v>
+        <v>11.75952233423905</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7174232691082244</v>
+        <v>0.9578774198381496</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.5040555764412202</v>
+        <v>1.441322196593012</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6997</v>
+        <v>7736</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>322.7966359718343</v>
+        <v>375.4404834088278</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>66</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.11087393705506</v>
+        <v>43.64434852898479</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.156839043433411</v>
+        <v>27.36738699384372</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6608146760035506</v>
+        <v>1.44608102704864</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.13019454964641</v>
+        <v>0.1456393288652932</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7842</v>
+        <v>7547</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>321.0162902647224</v>
+        <v>369.4596456692913</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.84399352210831</v>
+        <v>55.464918668506</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.91516003910239</v>
+        <v>25.60852815199996</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.097731287515145</v>
+        <v>0.3459645669291338</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.513853445557106</v>
+        <v>0.1785787302717194</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6936</v>
+        <v>6919</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>310.8155057520197</v>
+        <v>363.432004611126</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32.4</v>
+        <v>77.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>56.89576334430662</v>
+        <v>32.6457529966719</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.22757338874374</v>
+        <v>29.35759046997553</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.313501843678952</v>
+        <v>0.4697079789208124</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0678139143777811</v>
+        <v>0.4308944767342186</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7821</v>
+        <v>7750</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>310.3542756442301</v>
+        <v>361.1417718116325</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>36.9</v>
+        <v>1915</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.41156466483048</v>
+        <v>41.60214766673347</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>35.66988134577467</v>
+        <v>15.35126166101525</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.872107782621567</v>
+        <v>1.12077332553824</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0427356339603892</v>
+        <v>10.56163794212451</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7714</v>
+        <v>7856</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>308.0942750360705</v>
+        <v>360.8098086489869</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>169</v>
+        <v>3835</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.3502062534296</v>
+        <v>36.31332380901144</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23.22446020999554</v>
+        <v>12.54883144717722</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.147016214736046</v>
+        <v>2.151578047471147</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2765632062707066</v>
+        <v>-80.65921042144876</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7818</v>
+        <v>7805</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>307.4308490587295</v>
+        <v>351.593853940262</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>60.2</v>
+        <v>491</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.20855786376794</v>
+        <v>38.79340588729129</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.4678987538295</v>
+        <v>26.8014390547266</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.889033031435272</v>
+        <v>2.838598737424477</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1976654987968368</v>
+        <v>4.369308009996612</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6887</v>
+        <v>6907</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>305.6867314667099</v>
+        <v>342.7709492182713</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>36.5</v>
+        <v>181.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.43791836740232</v>
+        <v>45.90177964232763</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>34.40728872648467</v>
+        <v>16.25118803316159</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3932932752514553</v>
+        <v>0.2835132485385495</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2512748504957609</v>
+        <v>-0.509111356590281</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7749</v>
+        <v>6931</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>302.2606968586249</v>
+        <v>328.9712872360475</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>354</v>
+        <v>38.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.60182331702512</v>
+        <v>35.54148193989346</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.46478486684427</v>
+        <v>11.69377484760864</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.130116711686041</v>
+        <v>0.9939166400039116</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-2.790121586177793</v>
+        <v>-0.0639358979213048</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7738</v>
+        <v>7732</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.7208012606409</v>
+        <v>326.3265212043571</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>162</v>
+        <v>34.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.91398540273693</v>
+        <v>51.91674993366773</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.47528783908361</v>
+        <v>7.030744669778905</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8401988701392641</v>
+        <v>0.4626187525815778</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.6847760863569721</v>
+        <v>0.7485220746012249</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7855</v>
+        <v>7768</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>301.4777689447498</v>
+        <v>326.264316279618</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>41.4</v>
+        <v>292.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>22.87504610261987</v>
+        <v>50.55691333678696</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>58.75207589623036</v>
+        <v>26.27506445368565</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5595113137818786</v>
+        <v>0.7174232691082244</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.850016678802807</v>
+        <v>0.5040555754797937</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7728</v>
+        <v>6997</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>297.0566537120375</v>
+        <v>322.7966359718342</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>624</v>
+        <v>66</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.03724928145547</v>
+        <v>52.11087394434137</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.66251797186336</v>
+        <v>8.156838954311102</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2642228007976955</v>
+        <v>0.6608146760035506</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.191494717481193</v>
+        <v>1.130194549478162</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7740</v>
+        <v>7842</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>296.6452979623605</v>
+        <v>321.0162902647224</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>115</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.89927534144173</v>
+        <v>51.84399354121931</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>26.68354729771584</v>
+        <v>15.9151600391024</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3.288829540640118</v>
+        <v>1.097731287515145</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.349599330655566</v>
+        <v>-0.5138534467588443</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7791</v>
+        <v>6936</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>294.7819674299589</v>
+        <v>310.8155057520158</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>53</v>
+        <v>32.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>26.83259636059644</v>
+        <v>56.89576365297002</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.72036045541088</v>
+        <v>15.22757356774707</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.977962964738825</v>
+        <v>1.313501843678952</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.128783772434889</v>
+        <v>0.06781391426961721</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6962</v>
+        <v>7714</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>293.0554820071094</v>
+        <v>308.0942750360705</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.22292853808494</v>
+        <v>50.35020627577948</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.8519531468596</v>
+        <v>23.22446028735129</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5692481862778273</v>
+        <v>0.147016214736046</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.069086723675733</v>
+        <v>-0.2765632066312369</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7820</v>
+        <v>7818</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>291.0910570980333</v>
+        <v>307.4308490587295</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>23.1091009095545</v>
+        <v>43.20855795643821</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.05839562334934</v>
+        <v>14.4678987842299</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.0011124243899047</v>
+        <v>1.889033031435272</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-10.03211285143334</v>
+        <v>0.1976654985564799</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6965</v>
+        <v>6887</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>286.8155688352707</v>
+        <v>305.6867314667173</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.65760059074996</v>
+        <v>42.4379183426741</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46.70687375684927</v>
+        <v>34.40728871036207</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.200342706255794</v>
+        <v>0.3932932752514553</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1236861269863207</v>
+        <v>-0.2512748504236545</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7822</v>
+        <v>7749</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>285.4577856126686</v>
+        <v>302.2606968586249</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>925</v>
+        <v>354</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.24331101471548</v>
+        <v>40.60182273258212</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.43447267159423</v>
+        <v>21.46478531478618</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8185475009109529</v>
+        <v>1.130116711686041</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>3.161766237732653</v>
+        <v>-2.790121576804264</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7753</v>
+        <v>8024</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>285.3290048088081</v>
+        <v>297.1154062224044</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.85</v>
+        <v>12.95</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.6729739614404</v>
+        <v>53.9739130989688</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.10500350694856</v>
+        <v>18.09708899256923</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.238226827216114</v>
+        <v>1.760185118065357</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1041538058023653</v>
+        <v>0.0475338951634391</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6949</v>
+        <v>7728</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>285.1643450613371</v>
+        <v>297.0566537120376</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>46.7</v>
+        <v>624</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>25.98416138300256</v>
+        <v>50.03724929417221</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45.44809237212301</v>
+        <v>24.66251796581476</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.555496172948613</v>
+        <v>0.2642228007976955</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>31.85810539628119</v>
+        <v>1.191494716279458</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6951</v>
+        <v>7791</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>278.6505534687979</v>
+        <v>294.7819674299589</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>53</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>26.98754029630506</v>
+        <v>26.83259627743286</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>31.65624708538875</v>
+        <v>24.72036045541088</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5846671735056044</v>
+        <v>1.977962964738825</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0497257062213852</v>
+        <v>-0.128783772434889</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6967</v>
+        <v>6962</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>278.6178231886368</v>
+        <v>293.0554820071094</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>70.8</v>
+        <v>32</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.03473720722251</v>
+        <v>49.22292850245334</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.09975580796187</v>
+        <v>16.85195309776621</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2989080457239553</v>
+        <v>0.5692481862778273</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6808243578890584</v>
+        <v>0.06908672355556519</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7689</v>
+        <v>7820</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>274.8297912782464</v>
+        <v>291.0910570980297</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>154.5</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.22290381358862</v>
+        <v>23.10910072243369</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.94145434975584</v>
+        <v>15.05839609637641</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3764223576618292</v>
+        <v>0.0011124243899047</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4927140545002215</v>
+        <v>-10.03211284590538</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7722</v>
+        <v>7822</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>265.655472171428</v>
+        <v>285.4577856126686</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>265</v>
+        <v>925</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.41092081490652</v>
+        <v>50.24331100810276</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.13911557752183</v>
+        <v>18.43447272534626</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5196400801855945</v>
+        <v>0.8185475009109529</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.387066982879746</v>
+        <v>3.161766233166118</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6958</v>
+        <v>7753</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>265.5226067479907</v>
+        <v>285.3290048088081</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>17.05</v>
+        <v>35.85</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.78280004919139</v>
+        <v>45.67297417485723</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.90084926367908</v>
+        <v>10.1050034463154</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.312704672003566</v>
+        <v>1.238226827216114</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0441169149369277</v>
+        <v>0.1041538052255391</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6855</v>
+        <v>6951</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>264.3228070896759</v>
+        <v>278.6505534687978</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>110.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>52.22130595263592</v>
+        <v>26.98754022913928</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.84939377167283</v>
+        <v>31.65624709818636</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>4.889231863072374</v>
+        <v>0.5846671735056044</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>5.530426705512274</v>
+        <v>-0.049725706197347</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6890</v>
+        <v>6967</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>264.0416352018328</v>
+        <v>278.6178231886368</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>152</v>
+        <v>70.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.35160933602227</v>
+        <v>54.03473719550721</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.75952224984717</v>
+        <v>17.09975584068324</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9578774198381496</v>
+        <v>0.2989080457239553</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>1.441322199597364</v>
+        <v>0.6808243575525754</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7828</v>
+        <v>7689</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>258.4052635627925</v>
+        <v>274.8297912782464</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1830</v>
+        <v>154.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.21868719013552</v>
+        <v>34.22290381358862</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.80507576171192</v>
+        <v>18.94145434975584</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8833206614536219</v>
+        <v>0.3764223576618292</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-22.89852431077135</v>
+        <v>0.4927140545002215</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8034</v>
+        <v>6958</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>251.7628801235771</v>
+        <v>265.5226067479907</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>19.4</v>
+        <v>17.05</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.25739914886788</v>
+        <v>46.78280003639558</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.80243466398816</v>
+        <v>21.90084926995608</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4958102915562519</v>
+        <v>1.312704672003566</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1278121302236438</v>
+        <v>-0.0441169149249084</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7715</v>
+        <v>6855</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>249.5871488543673</v>
+        <v>264.3228070896759</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.8</v>
+        <v>110.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.72101268226475</v>
+        <v>52.22130594512792</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.29430173006481</v>
+        <v>7.849393493834665</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5514038283812792</v>
+        <v>4.889231863072374</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0065559625322137</v>
+        <v>5.530426705512274</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6952</v>
+        <v>7828</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>245.1554734389516</v>
+        <v>258.4052635627926</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>38.95</v>
+        <v>1830</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.11015844110335</v>
+        <v>47.21868715532006</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.511840137328209</v>
+        <v>16.80507574377367</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.62242552766274</v>
+        <v>0.8833206614536219</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.4855975149460361</v>
+        <v>-22.89852430620458</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6914</v>
+        <v>6969</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>236.7756187870102</v>
+        <v>253.9447008060246</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>118.5</v>
+        <v>30</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>30.92041813135308</v>
+        <v>40.13676717908693</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>36.21712706491477</v>
+        <v>11.50096641914868</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7319924034538533</v>
+        <v>0.4762100910718944</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.6505179178253817</v>
+        <v>-0.18430385870784</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7770</v>
+        <v>6854</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>231.700158375046</v>
+        <v>253.4580332348052</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>39</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.89643672802575</v>
+        <v>50.33739428258247</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.45229379569234</v>
+        <v>13.8108776670331</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5479234712579536</v>
+        <v>0.8557960619849023</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1883031467715994</v>
+        <v>0.2675493699035149</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6865</v>
+        <v>8034</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>230.4632472883038</v>
+        <v>251.7628801235685</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>26.4</v>
+        <v>19.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.99982845641908</v>
+        <v>42.25739939724672</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.46978243072262</v>
+        <v>15.80243481720054</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3977491892214042</v>
+        <v>0.4958102915562519</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3426341447609261</v>
+        <v>-0.1278121304279365</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6994</v>
+        <v>7715</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>228.8343428681776</v>
+        <v>249.5871488543673</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>29.1</v>
+        <v>26.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.11792452060094</v>
+        <v>36.72101262191632</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>32.05693445481604</v>
+        <v>23.29430178111281</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5642723924276757</v>
+        <v>0.5514038283812792</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5488206505136026</v>
+        <v>0.0065559625322137</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7780</v>
+        <v>6952</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>227.0997627920148</v>
+        <v>245.1554734389516</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>16.25</v>
+        <v>38.95</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.3310897675055</v>
+        <v>52.11015844438219</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.08752068597386</v>
+        <v>8.511840209463545</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.683161572518519</v>
+        <v>0.62242552766274</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0481527345384024</v>
+        <v>0.4855975148499021</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7760</v>
+        <v>6914</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>226.716418958484</v>
+        <v>236.7756187870102</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>32.8</v>
+        <v>118.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.582638457129</v>
+        <v>30.92041798361996</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25.92623112177285</v>
+        <v>36.21712706490621</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.006143844823679</v>
+        <v>0.7319924034538533</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0241175517712428</v>
+        <v>0.650517917945538</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7812</v>
+        <v>7770</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>稜研科技*-創</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>220.5649185502512</v>
+        <v>231.700158375046</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>39</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>31.74292650553771</v>
+        <v>48.89643661658216</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.39477757589916</v>
+        <v>12.45229404407697</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.956491855025118</v>
+        <v>0.5479234712579536</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.7662097179951308</v>
+        <v>-0.188303146290907</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6921</v>
+        <v>6865</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>219.3667903858186</v>
+        <v>230.4632472883038</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>26.4</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.49198389751804</v>
+        <v>49.99982856529907</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.1508057178233</v>
+        <v>13.46978245784915</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.288777745395745</v>
+        <v>0.3977491892214042</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.066123035752822</v>
+        <v>-0.3426341452416196</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6931</v>
+        <v>6994</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>218.9712872360474</v>
+        <v>228.8343428681776</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>38.2</v>
+        <v>29.1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>35.54148187848224</v>
+        <v>43.1179244674093</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.693774833872</v>
+        <v>32.05693446902298</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9939166400039116</v>
+        <v>0.5642723924276757</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0639358978612197</v>
+        <v>0.5488206501290511</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6996</v>
+        <v>7780</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>216.2022884286677</v>
+        <v>227.0997627920148</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>166</v>
+        <v>16.25</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.38148167511107</v>
+        <v>48.33108411064796</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.65646488943053</v>
+        <v>19.08753228323369</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.275397902592022</v>
+        <v>1.683161572518519</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0722470505717436</v>
+        <v>0.0481527375895958</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6928</v>
+        <v>7760</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>213.2963122637667</v>
+        <v>226.7164189584842</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>43.7</v>
+        <v>32.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>36.54980784170996</v>
+        <v>48.58263846774155</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.1809534642871</v>
+        <v>25.92623113299806</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.205248893263485</v>
+        <v>1.006143844823679</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1397422048622014</v>
+        <v>0.0241175517712428</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8032</v>
+        <v>7812</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>稜研科技*-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>189.7602197080397</v>
+        <v>220.5649185502512</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>35.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.60340068604905</v>
+        <v>31.74292649974049</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.99123182540133</v>
+        <v>23.39477757589916</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.234196742035008</v>
+        <v>0.956491855025118</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.07299054044205031</v>
+        <v>-0.7662097183316066</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7732</v>
+        <v>6921</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>186.3265212043571</v>
+        <v>219.3667903858186</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>34.05</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.91674992154597</v>
+        <v>51.49198389751804</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7.030744724146166</v>
+        <v>19.1508057178233</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4626187525815778</v>
+        <v>2.288777745395745</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.748522074781486</v>
+        <v>-1.066123035752822</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8024</v>
+        <v>6996</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>182.1154062224044</v>
+        <v>216.2022884286674</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12.95</v>
+        <v>166</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>53.97391305845785</v>
+        <v>39.38148166059386</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.09708897173195</v>
+        <v>17.65646498407068</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.760185118065357</v>
+        <v>1.275397902592022</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0475338952475619</v>
+        <v>-0.0722470514129467</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6969</v>
+        <v>6873</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>178.9447008060247</v>
+        <v>213.8729853448865</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>30</v>
+        <v>65.7</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.13676735078557</v>
+        <v>38.73487517554786</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.5009663551602</v>
+        <v>15.86789039337853</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4762100910718944</v>
+        <v>0.6105173910834312</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1843038586838067</v>
+        <v>-0.0834214744812893</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6899</v>
+        <v>6928</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>175.0289474987961</v>
+        <v>213.2963122637669</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>49.3</v>
+        <v>43.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.38316355419524</v>
+        <v>36.54980795755137</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>24.08062047842853</v>
+        <v>13.18095374009881</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.484853594110043</v>
+        <v>1.205248893263485</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0443080510447774</v>
+        <v>-0.1397422064725186</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6908</v>
+        <v>8032</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>154.0320024652504</v>
+        <v>189.7602197080398</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>26</v>
+        <v>35.7</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>25.1085984252219</v>
+        <v>46.60340084659468</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.18999717655545</v>
+        <v>13.99123205858451</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.429311060592962</v>
+        <v>1.234196742035008</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1938718619598787</v>
+        <v>0.07299053978109379</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7402</v>
+        <v>6899</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>153.9689216309633</v>
+        <v>175.0289474987873</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>99</v>
+        <v>49.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.00627010284661</v>
+        <v>44.38316364422457</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.29351911795063</v>
+        <v>24.08062051021365</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4685651947082845</v>
+        <v>1.484853594110043</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1910523389918585</v>
+        <v>0.044308050972676</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7803</v>
+        <v>6908</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>152.2375150255849</v>
+        <v>154.0320024652504</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16.8</v>
+        <v>26</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>26.72731321373107</v>
+        <v>25.10859875505612</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.0682940156434</v>
+        <v>16.18999718184229</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>3.123751502558493</v>
+        <v>1.429311060592962</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0725543233668164</v>
+        <v>-0.193871862368465</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6854</v>
+        <v>7402</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>143.4580332348053</v>
+        <v>153.9689216309633</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>50.33739461502287</v>
+        <v>41.00627016902274</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.81087767311764</v>
+        <v>16.29351913324615</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8557960619849023</v>
+        <v>0.4685651947082845</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.2675493695430039</v>
+        <v>0.1910523385592359</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7721</v>
+        <v>7803</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>137.8604645032655</v>
+        <v>152.2375150255849</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>60.7</v>
+        <v>16.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.33082860330539</v>
+        <v>26.72731349716631</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.84076366587766</v>
+        <v>19.06829408293046</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.092627775311996</v>
+        <v>3.123751502558493</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0029304220624933</v>
+        <v>-0.07255432340287039</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7786</v>
+        <v>7721</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>129.237063170422</v>
+        <v>137.8604645032718</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>115</v>
+        <v>60.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.07543757707408</v>
+        <v>45.33082851371208</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.03757408685959</v>
+        <v>19.84076366533982</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.05898984005551</v>
+        <v>1.092627775311996</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1043756401120947</v>
+        <v>-0.0029304222307325</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7705</v>
+        <v>7786</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>127.4378777730473</v>
+        <v>129.2370631704221</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>29.55</v>
+        <v>115</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.00624366229707</v>
+        <v>41.07543686680165</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.473775449546284</v>
+        <v>11.03757453065145</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5533148176856841</v>
+        <v>1.05898984005551</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0022530783585728</v>
+        <v>-0.1043756381893348</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6923</v>
+        <v>7705</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>123.9923993686425</v>
+        <v>127.4378777730471</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>29.55</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>37.11105317234726</v>
+        <v>37.00624414193488</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.12126663447686</v>
+        <v>9.473775449546284</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2531963640233894</v>
+        <v>0.5533148176856841</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.2405403776446961</v>
+        <v>-0.0022530785388311</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6873</v>
+        <v>6923</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>103.8729853448865</v>
+        <v>123.9923993686424</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>65.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.73487525887354</v>
+        <v>37.111053107483</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>15.86789043282544</v>
+        <v>12.12126666299852</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6105173910834312</v>
+        <v>0.2531963640233894</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.08342147400060181</v>
+        <v>-0.2405403775485568</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>41.40194355700782</v>
+        <v>41.40194350606301</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.80758935121374</v>
+        <v>15.80758938687611</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.2433415527030331</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-1.055275224080719</v>
+        <v>-1.055275223613498</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
